--- a/output/pdf_financials_xlsx/AFI.xlsx
+++ b/output/pdf_financials_xlsx/AFI.xlsx
@@ -1910,13 +1910,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>1.364161</v>
+        <v>7.488883</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>1.375086</v>
+        <v>7.719045</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>1.378525</v>
+        <v>7.722484</v>
       </c>
     </row>
     <row r="93">
@@ -3587,7 +3587,11 @@
           <t>Share-based payment reserve (Note 8)</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -3913,7 +3917,11 @@
           <t>Share-based payment reserve (Note 8)</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E34" s="5" t="n">
         <v>6.124722</v>
       </c>

--- a/output/pdf_financials_xlsx/AFI.xlsx
+++ b/output/pdf_financials_xlsx/AFI.xlsx
@@ -976,13 +976,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.002172</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.002906</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.00757</v>
       </c>
     </row>
     <row r="35">
@@ -1008,13 +1008,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.002172</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.002906</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.00757</v>
       </c>
     </row>
     <row r="37">
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.017197</v>
+        <v>0.015025</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.049163</v>
+        <v>0.046257</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.104978</v>
+        <v>0.09740799999999999</v>
       </c>
     </row>
     <row r="49">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4192,7 +4192,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E61" s="5" t="n">

--- a/output/pdf_financials_xlsx/AFI.xlsx
+++ b/output/pdf_financials_xlsx/AFI.xlsx
@@ -877,13 +877,13 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0</v>
+        <v>0.244782</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>0.221171</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>0.216146</v>
       </c>
     </row>
     <row r="29">
@@ -893,13 +893,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.669075</v>
+        <v>-0.424293</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.029121</v>
+        <v>-0.8079499999999999</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.654959</v>
+        <v>-1.438813</v>
       </c>
     </row>
     <row r="30">
@@ -4049,7 +4049,11 @@
           <t>Amortization – intangible assets (Note 5) $</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E38" s="5" t="n">
         <v>0.045216</v>
       </c>
@@ -4105,7 +4109,11 @@
           <t>Depreciation – property and equipment (Note 4)</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E40" s="5" t="n">
         <v>0.139613</v>
       </c>
@@ -4132,7 +4140,11 @@
           <t>Depreciation – right-of-use asset (Note 9(b))</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E41" s="5" t="n">
         <v>0.059953</v>
       </c>

--- a/output/pdf_financials_xlsx/AFI.xlsx
+++ b/output/pdf_financials_xlsx/AFI.xlsx
@@ -1510,7 +1510,7 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.0961</v>
       </c>
       <c r="C67" s="3" t="n">
         <v>0</v>
